--- a/Exam/gymtrackerpro/lib/controller/__tests__/it/workout-session-controller/createWorkoutSession-it-form.xlsx
+++ b/Exam/gymtrackerpro/lib/controller/__tests__/it/workout-session-controller/createWorkoutSession-it-form.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="62">
   <si>
     <t>Statement: createWorkoutSession(data: CreateWorkoutSessionInput, exercises: WorkoutSessionExerciseInput[]): Promise&lt;ActionResult&lt;WorkoutSessionWithExercises&gt;&gt; — validates both the session data and the exercises array with Zod, then delegates to workoutSessionService.createWorkoutSession().</t>
   </si>
@@ -83,14 +83,14 @@
   </si>
   <si>
     <t xml:space="preserve">Member seeded via userService.createMember(). Exercise seeded via exerciseService.createExercise().
-const data: CreateWorkoutSessionInput = { memberId: seededMember.id, date: "2024-06-01", duration: 60, notes: "Test session" }
-const exercises: WorkoutSessionExerciseInput[] = [{ exerciseId: seededExercise.id, sets: 3, reps: 10, weight: 50 }]</t>
-  </si>
-  <si>
-    <t>createWorkoutSession(data, exercises)</t>
-  </si>
-  <si>
-    <t>{ success: true, data: { id: defined, memberId: seededMember.id, duration: 60, exercises: [length 1] } }</t>
+const inputData: CreateWorkoutSessionInput = { memberId: seededMember.id, date: "2024-06-01", duration: 60, notes: "Test session" }
+const inputExercises: WorkoutSessionExerciseInput[] = [{ exerciseId: seededExercise.id, sets: 3, reps: 10, weight: 50 }]</t>
+  </si>
+  <si>
+    <t>createWorkoutSession(inputData, inputExercises)</t>
+  </si>
+  <si>
+    <t>{ success: true, data: { id: defined, memberId: seededMember.id, duration: 60, notes: "Test session", exercises: [length 1] } }</t>
   </si>
   <si>
     <t>One workout_sessions row and one workout_session_exercises row linked to it exist</t>
@@ -102,12 +102,12 @@
     <t>2</t>
   </si>
   <si>
-    <t xml:space="preserve">Member seeded via userService.createMember(). Two exercises seeded via exerciseService.createExercise().
-const data: CreateWorkoutSessionInput = { memberId: seededMember.id, date: "2024-06-01", duration: 45 }
-const exercises: WorkoutSessionExerciseInput[] = [{ exerciseId: exercise1.id, sets: 3, reps: 10, weight: 50 }, { exerciseId: exercise2.id, sets: 4, reps: 8, weight: 80 }]</t>
-  </si>
-  <si>
-    <t>{ success: true, data: { exercises: [length 2] } }</t>
+    <t xml:space="preserve">Member seeded via userService.createMember(). Two exercises seeded via exerciseService.createExercise(): benchPressExercise, deadliftExercise.
+const inputData: CreateWorkoutSessionInput = { memberId: seededMember.id, date: "2024-06-01", duration: 45 }
+const inputExercises: WorkoutSessionExerciseInput[] = [{ exerciseId: benchPressExercise.id, sets: 3, reps: 10, weight: 50 }, { exerciseId: deadliftExercise.id, sets: 4, reps: 8, weight: 80 }]</t>
+  </si>
+  <si>
+    <t>{ success: true, data: { exercises: [length 2, benchPressExercise and deadliftExercise present] } }</t>
   </si>
   <si>
     <t>One workout_sessions row and two workout_session_exercises rows linked to it exist</t>
@@ -117,8 +117,8 @@
   </si>
   <si>
     <t xml:space="preserve">Member seeded via userService.createMember().
-const data: CreateWorkoutSessionInput = { memberId: seededMember.id, date: "2024-06-01", duration: 60 }
-const exercises: WorkoutSessionExerciseInput[] = []</t>
+const inputData: CreateWorkoutSessionInput = { memberId: seededMember.id, date: "2024-06-01", duration: 60 }
+const inputExercises: WorkoutSessionExerciseInput[] = []</t>
   </si>
   <si>
     <t>{ success: false, message: defined non-empty string ("At least one exercise is required") }</t>
@@ -131,11 +131,11 @@
   </si>
   <si>
     <t xml:space="preserve">Empty database.
-const data = {} as unknown as CreateWorkoutSessionInput (all required fields missing)
-const exercises: WorkoutSessionExerciseInput[] = []</t>
-  </si>
-  <si>
-    <t>{ success: false, message: "Validation failed", errors: { memberId, date, duration: each defined } }</t>
+const inputData = {} as unknown as CreateWorkoutSessionInput
+const inputExercises: WorkoutSessionExerciseInput[] = []</t>
+  </si>
+  <si>
+    <t>{ success: false, message: "Validation failed", errors: { memberId: defined, date: defined, duration: defined } }</t>
   </si>
   <si>
     <t>No change</t>
@@ -145,11 +145,25 @@
   </si>
   <si>
     <t xml:space="preserve">Exercise seeded via exerciseService.createExercise(). No member in database.
-const data: CreateWorkoutSessionInput = { memberId: "00000000-0000-0000-0000-000000000000", date: "2024-06-01", duration: 60 }
-const exercises: WorkoutSessionExerciseInput[] = [{ exerciseId: seededExercise.id, sets: 3, reps: 10, weight: 50 }]</t>
+const inputData: CreateWorkoutSessionInput = { memberId: "00000000-0000-0000-0000-000000000000", date: "2024-06-01", duration: 60 }
+const inputExercises: WorkoutSessionExerciseInput[] = [{ exerciseId: seededExercise.id, sets: 3, reps: 10, weight: 50 }]</t>
   </si>
   <si>
     <t>{ success: false, message: defined non-empty string (NotFoundError message) }</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Member seeded via userService.createMember(). Exercise seeded via exerciseService.createExercise(). Prior call to createWorkoutSession() with memberId "00000000-0000-0000-0000-000000000000" executed and returned { success: false }.
+const inputData: CreateWorkoutSessionInput = { memberId: seededMember.id, date: "2024-06-01", duration: 60 }
+const inputExercises: WorkoutSessionExerciseInput[] = [{ exerciseId: seededExercise.id, sets: 3, reps: 10, weight: 50 }]</t>
+  </si>
+  <si>
+    <t>{ success: true, data: { memberId: seededMember.id } }</t>
+  </si>
+  <si>
+    <t>One workout_sessions row exists for seededMember; no row exists for the non-existent member</t>
   </si>
   <si>
     <t>Testing</t>
@@ -836,12 +850,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="80" customWidth="1"/>
-    <col min="4" max="4" width="41" customWidth="1"/>
+    <col min="4" max="4" width="51" customWidth="1"/>
     <col min="5" max="6" width="80" customWidth="1"/>
     <col min="7" max="7" width="17" customWidth="1"/>
   </cols>
@@ -892,7 +906,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" ht="95" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" ht="110" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -981,6 +995,29 @@
         <v>34</v>
       </c>
       <c r="G6" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" ht="110" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="6" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1009,17 +1046,17 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -1031,40 +1068,40 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G5" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="K5" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="L5" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="J5" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>48</v>
-      </c>
       <c r="M5" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1072,40 +1109,40 @@
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C6" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
